--- a/data/raw/balancesheet.xlsx
+++ b/data/raw/balancesheet.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Narendra\Desktop\nifty100_project\data\raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF58490-7B28-4CAA-889B-05D18CE4870D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C927B079-B588-4E79-A259-F2DC101C6191}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3348" yWindow="3348" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2616" yWindow="2616" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Balance Sheet" sheetId="1" r:id="rId1"/>
@@ -916,7 +916,7 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="10" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="10" customWidth="1"/>
